--- a/WalletDataUpgrade.xlsx
+++ b/WalletDataUpgrade.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SoapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FE05B2-A278-4B5B-80FC-5B45B004CD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14235"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddToken" sheetId="1" r:id="rId1"/>
@@ -230,13 +231,13 @@
     <t>pwd2325</t>
   </si>
   <si>
-    <t>12/25</t>
+    <t>12/29</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -290,12 +291,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -576,51 +576,51 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.59765625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="48" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="25.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="34" max="34" width="7.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="25.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -736,7 +736,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>52</v>
       </c>
@@ -811,7 +811,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>53</v>
       </c>
@@ -833,11 +833,10 @@
       <c r="H3" s="1">
         <v>256072691</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>59</v>
       </c>
       <c r="N3" s="2"/>
@@ -891,7 +890,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>54</v>
       </c>
@@ -913,11 +912,10 @@
       <c r="H4" s="1">
         <v>256072691</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="1" t="s">
         <v>59</v>
       </c>
       <c r="N4" s="2"/>
@@ -971,7 +969,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>55</v>
       </c>
@@ -993,11 +991,10 @@
       <c r="H5" s="1">
         <v>256072691</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="1" t="s">
         <v>65</v>
       </c>
       <c r="N5" s="2"/>
@@ -1054,10 +1051,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.45">
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="Q6" s="2"/>
@@ -1073,10 +1067,7 @@
       <c r="AH6" s="2"/>
       <c r="AL6" s="2"/>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.45">
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="Q7" s="2"/>
@@ -1092,10 +1083,7 @@
       <c r="AH7" s="2"/>
       <c r="AL7" s="2"/>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.45">
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="Q8" s="2"/>
